--- a/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. Papa arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
+          <t>Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. Papa arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse. Me voici. Tu vas vers papa, maman, ou la maîtresse. Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. Papa arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse.
+maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Florence cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Florence a cherché maman. Papa et la maîtresse sont aussi des adultes connus. Ses pieds étaient près. Ses mains tenaient le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Florence tient la main de maman. Elles marchent vers la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Florence cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Florence a cherché maman. Papa et la maîtresse sont aussi des adultes connus. Ses pieds étaient près. Ses mains tenaient le manteau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Florence tient la main de maman. Elles marchent vers la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Florence va vers maman à l'école</t>
+          <t>Les patères et la main de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les patères cliquent. Nina cherche dans le couloir. Elle va vers maman, près de la porte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. Papa arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse. Me voici. Tu vas vers papa, maman, ou la maîtresse. Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
+          <t>Les patères du couloir font un petit clic. Un manteau bleu pend encore. La capuche est un peu mouillée. Ça sent le savon, tout près. Le carrelage est lisse et clair. Un dessin jaune brille au mur. Dehors, une flaque brille. Nina vit avec papa et maman. C'est la sortie. En ce moment, Nina est à l'école. La maîtresse est près de la porte. Maman attend près du portail. Papa arrive aussi. Nina cherche. Maman ? Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Le manteau est doux, un peu chaud. Nina se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers maman. Nina marche vers le portail. Ses pieds restent près du mur. Nina va vers maman. Me voici, Nina. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. Me voici aussi. Papa ! Bravo, Nina. Tu es venue vers nous. Nina prend la main de maman. La main est chaude. Tu as fait du bon travail. On reste ensemble. Nina est calme. Le couloir sent encore le savon. La flaque brille toujours, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. Papa arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse.
-maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
-narrateur|Florence prend la main de maman. Elle est calme. Le couloir sent le savon.</t>
+          <t>narrateur|Les patères du couloir font un petit clic.
+narrateur|Un manteau bleu pend encore.
+narrateur|La capuche est un peu mouillée.
+narrateur|Ça sent le savon, tout près.
+narrateur|Le carrelage est lisse et clair.
+narrateur|Un dessin jaune brille au mur.
+narrateur|Dehors, une flaque brille.
+narrateur|Nina vit avec papa et maman.
+narrateur|C'est la sortie.
+narrateur|En ce moment, Nina est à l'école.
+narrateur|La maîtresse est près de la porte.
+narrateur|Maman attend près du portail.
+narrateur|Papa arrive aussi.
+narrateur|Nina cherche.
+enfant-f|Maman ?
+narrateur|Ses pieds restent près de la maîtresse.
+narrateur|Ses mains tiennent son manteau.
+narrateur|Le manteau est doux, un peu chaud.
+narrateur|Nina se souvient.
+narrateur|On va vers papa.
+narrateur|On va vers maman.
+narrateur|On va vers la maîtresse.
+enfant-f|Je vais vers maman.
+narrateur|Nina marche vers le portail.
+narrateur|Ses pieds restent près du mur.
+narrateur|Nina va vers maman.
+maman|Me voici, Nina.
+enfant-f|Je t'ai cherchée.
+maman|Tu vas vers papa, maman, ou la maîtresse.
+maman|Bravo.
+maman|Tu es venue vers maman.
+papa|Me voici aussi.
+enfant-f|Papa !
+papa|Bravo, Nina.
+papa|Tu es venue vers nous.
+narrateur|Nina prend la main de maman.
+narrateur|La main est chaude.
+maman|Tu as fait du bon travail.
+maman|On reste ensemble.
+narrateur|Nina est calme.
+narrateur|Le couloir sent encore le savon.
+narrateur|La flaque brille toujours, dehors.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Florence cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>Nina cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Florence cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>narrateur|Nina cherche quelqu'un.
+narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Florence a cherché maman. Papa et la maîtresse sont aussi des adultes connus. Ses pieds étaient près. Ses mains tenaient le manteau.</t>
+          <t>Nina a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Nina. Papa et la maîtresse sont aussi des adultes connus. Tes pieds étaient près. Tes mains tenaient le manteau. La maîtresse était près de la porte. Oui. Nina tient encore la main de maman. Le savon sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1730,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Florence a cherché maman. Papa et la maîtresse sont aussi des adultes connus. Ses pieds étaient près. Ses mains tenaient le manteau.</t>
+          <t>narrateur|Nina a cherché maman.
+narrateur|Elle est allée vers maman.
+maman|Tu es venue vers moi ?
+enfant-f|Oui.
+enfant-f|Vers maman.
+maman|Bravo, Nina.
+maman|Papa et la maîtresse sont aussi des adultes connus.
+papa|Tes pieds étaient près.
+papa|Tes mains tenaient le manteau.
+enfant-f|La maîtresse était près de la porte.
+papa|Oui.
+narrateur|Nina tient encore la main de maman.
+narrateur|Le savon sent encore, tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Florence tient la main de maman. Elles marchent vers la porte.</t>
+          <t>Nina tient la main de maman. Elles marchent vers la porte. Tu as ton manteau ? Oui, papa. Tu as fini, Nina ? Oui. Bravo. La maîtresse fait un petit signe. L'air de dehors est frais. La flaque brille. Oui. On rentre ensemble. Les bottes de Nina font un petit bruit. Papa porte le sac d'école. On va vers la maison ? Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,7 +1914,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Florence tient la main de maman. Elles marchent vers la porte.</t>
+          <t>narrateur|Nina tient la main de maman.
+narrateur|Elles marchent vers la porte.
+papa|Tu as ton manteau ?
+enfant-f|Oui, papa.
+maman|Tu as fini, Nina ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|La maîtresse fait un petit signe.
+narrateur|L'air de dehors est frais.
+enfant-f|La flaque brille.
+maman|Oui.
+maman|On rentre ensemble.
+narrateur|Les bottes de Nina font un petit bruit.
+narrateur|Papa porte le sac d'école.
+papa|On va vers la maison ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1878,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le couloir sent le savon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis allée vers maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le couloir sent le savon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les patères du couloir font un petit clic. Un manteau bleu pend encore. La capuche est un peu mouillée. Ça sent le savon, tout près. Le carrelage est lisse et clair. Un dessin jaune brille au mur. Dehors, une flaque brille. Nina vit avec papa et maman. C'est la sortie. En ce moment, Nina est à l'école. La maîtresse est près de la porte. Maman attend près du portail. Papa arrive aussi. Nina cherche. Maman ? Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Le manteau est doux, un peu chaud. Nina se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers maman. Nina marche vers le portail. Ses pieds restent près du mur. Nina va vers maman. Me voici, Nina. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. Me voici aussi. Papa ! Bravo, Nina. Tu es venue vers nous. Nina prend la main de maman. La main est chaude. Tu as fait du bon travail. On reste ensemble. Nina est calme. Le couloir sent encore le savon. La flaque brille toujours, dehors.</t>
+          <t>Les patères du couloir font un petit clic. Un manteau bleu pend encore. La capuche est un peu mouillée. Ça sent le savon, tout près. Le carrelage est lisse et clair. Un dessin jaune brille au mur. Dehors, une flaque brille. Nina vit avec papa et maman. C'est la sortie. En ce moment, Nina est à l'école. La maîtresse est près de la porte. Maman attend près du portail. Papa arrive aussi. Nina cherche. Maman ? Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Le manteau est doux, un peu chaud. Nina se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers maman. Nina marche vers le portail. Ses pieds restent près du mur. Nina va vers maman. Me voici, Nina. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. Me voici aussi. Papa ! Bravo, Nina. Tu es venue vers nous. Nina prend la main de maman. La main est chaude. On reste ensemble. Nina est calme. Le couloir sent encore le savon. La flaque brille toujours, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Florence est à l'école. C'est la sortie. La maîtresse est près de la porte. Maman est là. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; arrive aussi. Florence cherche. Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Florence va vers maman. Elle va vers papa. Elle va vers la maîtresse. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Florence prend la main de maman. Elle est calme. Le couloir sent le savon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les patères du couloir font un petit clic. Un manteau bleu pend encore. La capuche est un peu mouillée. Ça sent le savon, tout près. Le carrelage est lisse et clair. Un dessin jaune brille au mur. Dehors, une flaque brille. Nina vit avec papa et maman. C'est la sortie. En ce moment, Nina est à l'école. La maîtresse est près de la porte. Maman attend près du portail. Papa arrive aussi. Nina cherche. Maman ? Ses pieds restent près de la maîtresse. Ses mains tiennent son manteau. Le manteau est doux, un peu chaud. Nina se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers maman. Nina marche vers le portail. Ses pieds restent près du mur. Nina va vers maman. Me voici, Nina. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. Me voici aussi. Papa ! Bravo, Nina. Tu es venue vers nous. Nina prend la main de maman. La main est chaude. On reste ensemble. Nina est calme. Le couloir sent encore le savon. La flaque brille toujours, dehors.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,14 +1361,12 @@
 papa|Tu es venue vers nous.
 narrateur|Nina prend la main de maman.
 narrateur|La main est chaude.
-maman|Tu as fait du bon travail.
 maman|On reste ensemble.
 narrateur|Nina est calme.
 narrateur|Le couloir sent encore le savon.
 narrateur|La flaque brille toujours, dehors.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1398,7 +1396,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Florence cherche quelqu'un. Vers qui va-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1557,7 +1555,6 @@
 narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1587,7 +1584,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Florence a cherché maman. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; et la maîtresse sont aussi des adultes connus. Ses pieds étaient près. Ses mains tenaient le manteau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Nina. Papa et la maîtresse sont aussi des adultes connus. Tes pieds étaient près. Tes mains tenaient le manteau. La maîtresse était près de la porte. Oui. Nina tient encore la main de maman. Le savon sent encore, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,7 +1742,6 @@
 narrateur|Le savon sent encore, tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Florence tient la main de &lt;emphasis level="moderate"&gt;maman&lt;/emphasis&gt;. Elles marchent vers la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina tient la main de maman. Elles marchent vers la porte. Tu as ton manteau ? Oui, papa. Tu as fini, Nina ? Oui. Bravo. La maîtresse fait un petit signe. L'air de dehors est frais. La flaque brille. Oui. On rentre ensemble. Les bottes de Nina font un petit bruit. Papa porte le sac d'école. On va vers la maison ? Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1928,6 @@
 enfant-f|Oui.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le couloir sent le savon. L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Le couloir sent le savon.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis allée vers maman. Bravo. Le couloir sent le savon.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2094,9 @@
         <is>
           <t>enfant-f|Je suis allée vers maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le couloir sent le savon.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le couloir sent le savon.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école, sortie</t>
+          <t>école, couloir de sortie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Florence, maman, papa, la maîtresse</t>
+          <t>Nina, maman, papa, la maîtresse</t>
         </is>
       </c>
     </row>
